--- a/samples/N_科目余额表.xlsx
+++ b/samples/N_科目余额表.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -508,19 +508,19 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>380000</v>
+        <v>520000</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1200000</v>
+        <v>1800000</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1270000</v>
+        <v>2100000</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>450000</v>
+        <v>820000</v>
       </c>
     </row>
     <row r="3">
@@ -531,26 +531,26 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>其他应付款-押金保证金</t>
+          <t>其他应付款-押金</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>250000</v>
+        <v>300000</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>520000</v>
+        <v>900000</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>270000</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="4">
@@ -561,26 +561,26 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>其他应付款-代扣代缴</t>
+          <t>其他应付款-保证金</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>80000</v>
+        <v>150000</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>400000</v>
+        <v>600000</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>410000</v>
+        <v>700000</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>90000</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="5">
@@ -591,7 +591,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>其他应付款-其他</t>
+          <t>其他应付款-代扣代缴</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -604,13 +604,43 @@
         <v>300000</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>340000</v>
+        <v>400000</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>90000</v>
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>224104</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>其他应付款-其他</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>20000</v>
       </c>
     </row>
   </sheetData>
